--- a/data/TX-123BT/Power_ThermalGen.xlsx
+++ b/data/TX-123BT/Power_ThermalGen.xlsx
@@ -1624,10 +1624,10 @@
         <v>7290</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>894.24</v>
@@ -1727,10 +1727,10 @@
         <v>4104</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="14" t="n">
         <v>170.58</v>
@@ -1830,10 +1830,10 @@
         <v>648</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>132.16</v>
@@ -1933,10 +1933,10 @@
         <v>2691.6</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="14" t="n">
         <v>98.78</v>
@@ -2036,10 +2036,10 @@
         <v>4605.6</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="14" t="n">
         <v>213.19</v>
@@ -2139,10 +2139,10 @@
         <v>3080.4</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="14" t="n">
         <v>392.6</v>
@@ -2242,10 +2242,10 @@
         <v>2517</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="14" t="n">
         <v>99.29000000000001</v>
@@ -2345,10 +2345,10 @@
         <v>4983</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="14" t="n">
         <v>213.81</v>
@@ -2448,10 +2448,10 @@
         <v>1086</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>51.91</v>
@@ -2551,10 +2551,10 @@
         <v>10640.4</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="14" t="n">
         <v>379.74</v>
@@ -2654,10 +2654,10 @@
         <v>3801</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="14" t="n">
         <v>145.6</v>
@@ -2757,10 +2757,10 @@
         <v>1252.2</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="14" t="n">
         <v>278.82</v>
@@ -2860,10 +2860,10 @@
         <v>211.2</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="14" t="n">
         <v>12.32</v>
@@ -2963,10 +2963,10 @@
         <v>462</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="14" t="n">
         <v>28.06</v>
@@ -3066,10 +3066,10 @@
         <v>3237</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="14" t="n">
         <v>94.69</v>
@@ -3169,10 +3169,10 @@
         <v>1746.6</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="14" t="n">
         <v>241.92</v>
@@ -3272,10 +3272,10 @@
         <v>14563.8</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>512.1799999999999</v>
@@ -3375,10 +3375,10 @@
         <v>2434.2</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="14" t="n">
         <v>712.98</v>
@@ -3478,10 +3478,10 @@
         <v>1863</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="14" t="n">
         <v>299.88</v>
@@ -3581,10 +3581,10 @@
         <v>159.6</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="14" t="n">
         <v>14.39</v>
@@ -3684,10 +3684,10 @@
         <v>1160.4</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>41.47</v>
@@ -3787,10 +3787,10 @@
         <v>708</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>21.08</v>
@@ -3890,10 +3890,10 @@
         <v>389.4</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="14" t="n">
         <v>23.04</v>
@@ -3993,10 +3993,10 @@
         <v>726.6</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="14" t="n">
         <v>16.9</v>
@@ -4096,10 +4096,10 @@
         <v>8652</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>297.77</v>
@@ -4199,10 +4199,10 @@
         <v>4332.6</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="14" t="n">
         <v>333.2</v>
@@ -4302,10 +4302,10 @@
         <v>2785.8</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="14" t="n">
         <v>135.52</v>
@@ -4405,10 +4405,10 @@
         <v>3174</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="14" t="n">
         <v>645.5700000000001</v>
@@ -4508,10 +4508,10 @@
         <v>1678.2</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="14" t="n">
         <v>42.94</v>
@@ -4611,10 +4611,10 @@
         <v>2715</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="14" t="n">
         <v>42.81</v>
@@ -4714,10 +4714,10 @@
         <v>3547.8</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="14" t="n">
         <v>60.32</v>
@@ -4817,10 +4817,10 @@
         <v>121.2</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="14" t="n">
         <v>0</v>
@@ -4920,10 +4920,10 @@
         <v>1218.6</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="14" t="n">
         <v>107.02</v>
@@ -5023,10 +5023,10 @@
         <v>8877.6</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="14" t="n">
         <v>482.16</v>
@@ -5126,10 +5126,10 @@
         <v>3243</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="14" t="n">
         <v>252</v>
@@ -5229,10 +5229,10 @@
         <v>640.8</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="14" t="n">
         <v>0</v>
@@ -5332,10 +5332,10 @@
         <v>1182</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="14" t="n">
         <v>0</v>
@@ -5435,10 +5435,10 @@
         <v>8056.8</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="14" t="n">
         <v>211.33</v>
@@ -5538,10 +5538,10 @@
         <v>1378.2</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="14" t="n">
         <v>94.08</v>
@@ -5641,10 +5641,10 @@
         <v>8125.8</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="14" t="n">
         <v>996.76</v>
@@ -5744,10 +5744,10 @@
         <v>403.2</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="14" t="n">
         <v>29.4</v>
@@ -5847,10 +5847,10 @@
         <v>426</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="14" t="n">
         <v>31.95</v>
@@ -5950,10 +5950,10 @@
         <v>3160.2</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="14" t="n">
         <v>346.47</v>
@@ -6053,10 +6053,10 @@
         <v>1113</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="14" t="n">
         <v>53.04</v>
@@ -6156,10 +6156,10 @@
         <v>831</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="14" t="n">
         <v>31.95</v>
@@ -6259,10 +6259,10 @@
         <v>1872</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="14" t="n">
         <v>36.1</v>
@@ -6362,10 +6362,10 @@
         <v>955.2</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="14" t="n">
         <v>140</v>
@@ -6465,10 +6465,10 @@
         <v>453</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="14" t="n">
         <v>35.27</v>
@@ -6568,10 +6568,10 @@
         <v>1456.8</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="14" t="n">
         <v>47.93</v>
@@ -6671,10 +6671,10 @@
         <v>7157.4</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="14" t="n">
         <v>511.39</v>
@@ -6774,10 +6774,10 @@
         <v>4069.8</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="14" t="n">
         <v>113.38</v>
@@ -6877,10 +6877,10 @@
         <v>492</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="14" t="n">
         <v>0</v>
@@ -6980,10 +6980,10 @@
         <v>2148.6</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="14" t="n">
         <v>26.94</v>
@@ -7083,10 +7083,10 @@
         <v>3624.6</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="14" t="n">
         <v>44.52</v>
@@ -7186,10 +7186,10 @@
         <v>2377.2</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="14" t="n">
         <v>42.6</v>
@@ -7289,10 +7289,10 @@
         <v>3589.8</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="14" t="n">
         <v>42.94</v>
@@ -7392,10 +7392,10 @@
         <v>229.8</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="14" t="n">
         <v>26.52</v>
@@ -7495,10 +7495,10 @@
         <v>630.6</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="14" t="n">
         <v>38.7</v>
@@ -7598,10 +7598,10 @@
         <v>38.4</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="14" t="n">
         <v>0</v>
@@ -7701,10 +7701,10 @@
         <v>11.4</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="14" t="n">
         <v>0</v>
@@ -7804,10 +7804,10 @@
         <v>106.8</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="14" t="n">
         <v>0</v>
@@ -7907,10 +7907,10 @@
         <v>556.8</v>
       </c>
       <c r="K69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="14" t="n">
         <v>0</v>
@@ -8010,10 +8010,10 @@
         <v>206.4</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="14" t="n">
         <v>0</v>
@@ -8113,10 +8113,10 @@
         <v>3802.2</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="14" t="n">
         <v>308.26</v>
@@ -8216,10 +8216,10 @@
         <v>3993.6</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="14" t="n">
         <v>547.74</v>
@@ -8319,10 +8319,10 @@
         <v>12469.2</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="14" t="n">
         <v>432.22</v>
@@ -8422,10 +8422,10 @@
         <v>3237</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="14" t="n">
         <v>200.26</v>
@@ -8525,10 +8525,10 @@
         <v>6800.4</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="14" t="n">
         <v>234.08</v>
@@ -8628,10 +8628,10 @@
         <v>2521.8</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="14" t="n">
         <v>397.13</v>
@@ -8731,10 +8731,10 @@
         <v>15269.4</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="14" t="n">
         <v>1036.45</v>
@@ -8834,10 +8834,10 @@
         <v>934.8</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="14" t="n">
         <v>620.65</v>
@@ -8937,10 +8937,10 @@
         <v>13779</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="14" t="n">
         <v>449.79</v>
@@ -9040,10 +9040,10 @@
         <v>387</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="14" t="n">
         <v>55.94</v>
@@ -9143,10 +9143,10 @@
         <v>12882</v>
       </c>
       <c r="K81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="14" t="n">
         <v>526.1799999999999</v>
@@ -9246,10 +9246,10 @@
         <v>9390</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>922.6799999999999</v>
@@ -9349,10 +9349,10 @@
         <v>16966.8</v>
       </c>
       <c r="K83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="14" t="n">
         <v>1108.89</v>
@@ -9452,10 +9452,10 @@
         <v>6364.2</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>0</v>
@@ -9555,10 +9555,10 @@
         <v>3172.2</v>
       </c>
       <c r="K85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="14" t="n">
         <v>319.2</v>
@@ -9658,10 +9658,10 @@
         <v>5683.2</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="14" t="n">
         <v>553.05</v>
@@ -9761,10 +9761,10 @@
         <v>8480.4</v>
       </c>
       <c r="K87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="14" t="n">
         <v>580.16</v>
@@ -9864,10 +9864,10 @@
         <v>5442.6</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="14" t="n">
         <v>612.7</v>
@@ -9967,10 +9967,10 @@
         <v>2920.2</v>
       </c>
       <c r="K89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="14" t="n">
         <v>417.76</v>
@@ -10070,10 +10070,10 @@
         <v>27458.4</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="14" t="n">
         <v>971.04</v>
@@ -10173,10 +10173,10 @@
         <v>14328.6</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="14" t="n">
         <v>716.8</v>
@@ -10276,10 +10276,10 @@
         <v>574.2</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>199.31</v>
@@ -10379,10 +10379,10 @@
         <v>9565.799999999999</v>
       </c>
       <c r="K93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="14" t="n">
         <v>281.28</v>
@@ -10482,10 +10482,10 @@
         <v>3690</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>441.5</v>
@@ -10585,10 +10585,10 @@
         <v>7170.6</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="14" t="n">
         <v>449.79</v>
@@ -10688,10 +10688,10 @@
         <v>5788.8</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="14" t="n">
         <v>295.77</v>
@@ -10791,10 +10791,10 @@
         <v>2700.6</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="14" t="n">
         <v>86.18000000000001</v>
@@ -10894,10 +10894,10 @@
         <v>6644.4</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="14" t="n">
         <v>275.22</v>
@@ -10997,10 +10997,10 @@
         <v>1964.4</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="14" t="n">
         <v>300.38</v>
@@ -11100,10 +11100,10 @@
         <v>1474.2</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="14" t="n">
         <v>128.8</v>
@@ -11203,10 +11203,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="14" t="n">
         <v>16.31</v>
@@ -11306,10 +11306,10 @@
         <v>3078</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>517.33</v>
@@ -11409,10 +11409,10 @@
         <v>162.6</v>
       </c>
       <c r="K103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="14" t="n">
         <v>26.88</v>
@@ -11512,10 +11512,10 @@
         <v>10652.4</v>
       </c>
       <c r="K104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="14" t="n">
         <v>456.4</v>
@@ -11615,10 +11615,10 @@
         <v>3478.8</v>
       </c>
       <c r="K105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="14" t="n">
         <v>409.33</v>
@@ -11718,10 +11718,10 @@
         <v>936.6</v>
       </c>
       <c r="K106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="14" t="n">
         <v>253.79</v>
@@ -11821,10 +11821,10 @@
         <v>2715.6</v>
       </c>
       <c r="K107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="14" t="n">
         <v>0</v>
@@ -11924,10 +11924,10 @@
         <v>1450.8</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="14" t="n">
         <v>57.51</v>
@@ -12027,10 +12027,10 @@
         <v>819</v>
       </c>
       <c r="K109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="14" t="n">
         <v>666.34</v>
@@ -12130,10 +12130,10 @@
         <v>156</v>
       </c>
       <c r="K110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="14" t="n">
         <v>5.19</v>
@@ -12233,10 +12233,10 @@
         <v>3368.4</v>
       </c>
       <c r="K111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="14" t="n">
         <v>514.25</v>
@@ -12336,10 +12336,10 @@
         <v>27196.2</v>
       </c>
       <c r="K112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="14" t="n">
         <v>787.54</v>
@@ -12439,10 +12439,10 @@
         <v>466.8</v>
       </c>
       <c r="K113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="14" t="n">
         <v>57.06</v>
@@ -12542,10 +12542,10 @@
         <v>2098.8</v>
       </c>
       <c r="K114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="14" t="n">
         <v>526.23</v>
@@ -12645,10 +12645,10 @@
         <v>8725.799999999999</v>
       </c>
       <c r="K115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="14" t="n">
         <v>360.42</v>
@@ -12748,10 +12748,10 @@
         <v>61855.8</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="14" t="n">
         <v>1867.91</v>
@@ -12851,10 +12851,10 @@
         <v>227.4</v>
       </c>
       <c r="K117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="14" t="n">
         <v>8.4</v>
@@ -12954,10 +12954,10 @@
         <v>4406.4</v>
       </c>
       <c r="K118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="14" t="n">
         <v>658.5599999999999</v>
@@ -13057,10 +13057,10 @@
         <v>5078.4</v>
       </c>
       <c r="K119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="14" t="n">
         <v>836.66</v>
@@ -13160,10 +13160,10 @@
         <v>6370.8</v>
       </c>
       <c r="K120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="14" t="n">
         <v>211.06</v>
@@ -13263,10 +13263,10 @@
         <v>2863.8</v>
       </c>
       <c r="K121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="14" t="n">
         <v>120.51</v>
@@ -13366,10 +13366,10 @@
         <v>11926.8</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="14" t="n">
         <v>386.06</v>
@@ -13469,10 +13469,10 @@
         <v>1468.8</v>
       </c>
       <c r="K123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="14" t="n">
         <v>191.06</v>
@@ -13572,10 +13572,10 @@
         <v>9572.4</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="14" t="n">
         <v>609.39</v>
@@ -13675,10 +13675,10 @@
         <v>6314.4</v>
       </c>
       <c r="K125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="14" t="n">
         <v>434.31</v>
@@ -13778,10 +13778,10 @@
         <v>2530.8</v>
       </c>
       <c r="K126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="14" t="n">
         <v>128.58</v>
@@ -13881,10 +13881,10 @@
         <v>3376.8</v>
       </c>
       <c r="K127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="14" t="n">
         <v>415.67</v>
@@ -13984,10 +13984,10 @@
         <v>6669.6</v>
       </c>
       <c r="K128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="14" t="n">
         <v>672.9</v>
@@ -14087,10 +14087,10 @@
         <v>463.2</v>
       </c>
       <c r="K129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="14" t="n">
         <v>289.52</v>
@@ -14190,10 +14190,10 @@
         <v>2230.2</v>
       </c>
       <c r="K130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="14" t="n">
         <v>147.62</v>
@@ -14293,10 +14293,10 @@
         <v>598.2</v>
       </c>
       <c r="K131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="14" t="n">
         <v>24.75</v>
@@ -14396,10 +14396,10 @@
         <v>2652.6</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="14" t="n">
         <v>95.42</v>
@@ -14499,10 +14499,10 @@
         <v>790.2</v>
       </c>
       <c r="K133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="14" t="n">
         <v>448.56</v>
@@ -14602,10 +14602,10 @@
         <v>13406.4</v>
       </c>
       <c r="K134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="14" t="n">
         <v>504.31</v>
@@ -14705,10 +14705,10 @@
         <v>8152.8</v>
       </c>
       <c r="K135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="14" t="n">
         <v>313.04</v>
@@ -14808,10 +14808,10 @@
         <v>1092</v>
       </c>
       <c r="K136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="14" t="n">
         <v>23.5</v>
@@ -14911,10 +14911,10 @@
         <v>1350</v>
       </c>
       <c r="K137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="14" t="n">
         <v>17.2</v>
@@ -15014,10 +15014,10 @@
         <v>2592</v>
       </c>
       <c r="K138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>45.2</v>
@@ -15117,10 +15117,10 @@
         <v>1344</v>
       </c>
       <c r="K139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="14" t="n">
         <v>11.8</v>
@@ -15220,10 +15220,10 @@
         <v>2112</v>
       </c>
       <c r="K140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>23.5</v>
@@ -15323,10 +15323,10 @@
         <v>522</v>
       </c>
       <c r="K141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="14" t="n">
         <v>3.6</v>
@@ -15426,10 +15426,10 @@
         <v>948</v>
       </c>
       <c r="K142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="14" t="n">
         <v>6.7</v>
@@ -15529,10 +15529,10 @@
         <v>1698</v>
       </c>
       <c r="K143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="14" t="n">
         <v>15.2</v>
@@ -15632,10 +15632,10 @@
         <v>1344</v>
       </c>
       <c r="K144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="14" t="n">
         <v>13.5</v>
@@ -15735,10 +15735,10 @@
         <v>912</v>
       </c>
       <c r="K145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" s="14" t="n">
         <v>15.6</v>
@@ -16709,10 +16709,10 @@
         <v>7290</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>894.24</v>
@@ -16812,10 +16812,10 @@
         <v>4104</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="14" t="n">
         <v>170.58</v>
@@ -16915,10 +16915,10 @@
         <v>648</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>132.16</v>
@@ -17018,10 +17018,10 @@
         <v>2691.6</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="14" t="n">
         <v>98.78</v>
@@ -17121,10 +17121,10 @@
         <v>4605.6</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="14" t="n">
         <v>213.19</v>
@@ -17224,10 +17224,10 @@
         <v>3080.4</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="14" t="n">
         <v>392.6</v>
@@ -17327,10 +17327,10 @@
         <v>2517</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="14" t="n">
         <v>99.29000000000001</v>
@@ -17430,10 +17430,10 @@
         <v>4983</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="14" t="n">
         <v>213.81</v>
@@ -17533,10 +17533,10 @@
         <v>1086</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>51.91</v>
@@ -17636,10 +17636,10 @@
         <v>10640.4</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="14" t="n">
         <v>379.74</v>
@@ -17739,10 +17739,10 @@
         <v>3801</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="14" t="n">
         <v>145.6</v>
@@ -17842,10 +17842,10 @@
         <v>1252.2</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="14" t="n">
         <v>278.82</v>
@@ -17945,10 +17945,10 @@
         <v>211.2</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="14" t="n">
         <v>12.32</v>
@@ -18048,10 +18048,10 @@
         <v>462</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="14" t="n">
         <v>28.06</v>
@@ -18151,10 +18151,10 @@
         <v>3237</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="14" t="n">
         <v>94.69</v>
@@ -18254,10 +18254,10 @@
         <v>1746.6</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="14" t="n">
         <v>241.92</v>
@@ -18357,10 +18357,10 @@
         <v>14563.8</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>512.1799999999999</v>
@@ -18460,10 +18460,10 @@
         <v>2434.2</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="14" t="n">
         <v>712.98</v>
@@ -18563,10 +18563,10 @@
         <v>1863</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="14" t="n">
         <v>299.88</v>
@@ -18666,10 +18666,10 @@
         <v>159.6</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="14" t="n">
         <v>14.39</v>
@@ -18769,10 +18769,10 @@
         <v>1160.4</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>41.47</v>
@@ -18872,10 +18872,10 @@
         <v>708</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>21.08</v>
@@ -18975,10 +18975,10 @@
         <v>389.4</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="14" t="n">
         <v>23.04</v>
@@ -19078,10 +19078,10 @@
         <v>726.6</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="14" t="n">
         <v>16.9</v>
@@ -19181,10 +19181,10 @@
         <v>8652</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>297.77</v>
@@ -19284,10 +19284,10 @@
         <v>4332.6</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="14" t="n">
         <v>333.2</v>
@@ -19387,10 +19387,10 @@
         <v>2785.8</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="14" t="n">
         <v>135.52</v>
@@ -19490,10 +19490,10 @@
         <v>3174</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="14" t="n">
         <v>645.5700000000001</v>
@@ -19593,10 +19593,10 @@
         <v>1678.2</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="14" t="n">
         <v>42.94</v>
@@ -19696,10 +19696,10 @@
         <v>2715</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="14" t="n">
         <v>42.81</v>
@@ -19799,10 +19799,10 @@
         <v>3547.8</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="14" t="n">
         <v>60.32</v>
@@ -19902,10 +19902,10 @@
         <v>121.2</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="14" t="n">
         <v>0</v>
@@ -20005,10 +20005,10 @@
         <v>1218.6</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="14" t="n">
         <v>107.02</v>
@@ -20108,10 +20108,10 @@
         <v>8877.6</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="14" t="n">
         <v>482.16</v>
@@ -20211,10 +20211,10 @@
         <v>3243</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="14" t="n">
         <v>252</v>
@@ -20314,10 +20314,10 @@
         <v>640.8</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="14" t="n">
         <v>0</v>
@@ -20417,10 +20417,10 @@
         <v>1182</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="14" t="n">
         <v>0</v>
@@ -20520,10 +20520,10 @@
         <v>8056.8</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="14" t="n">
         <v>211.33</v>
@@ -20623,10 +20623,10 @@
         <v>1378.2</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="14" t="n">
         <v>94.08</v>
@@ -20726,10 +20726,10 @@
         <v>8125.8</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="14" t="n">
         <v>996.76</v>
@@ -20829,10 +20829,10 @@
         <v>403.2</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="14" t="n">
         <v>29.4</v>
@@ -20932,10 +20932,10 @@
         <v>426</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="14" t="n">
         <v>31.95</v>
@@ -21035,10 +21035,10 @@
         <v>3160.2</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="14" t="n">
         <v>346.47</v>
@@ -21138,10 +21138,10 @@
         <v>1113</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="14" t="n">
         <v>53.04</v>
@@ -21241,10 +21241,10 @@
         <v>831</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="14" t="n">
         <v>31.95</v>
@@ -21344,10 +21344,10 @@
         <v>1872</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="14" t="n">
         <v>36.1</v>
@@ -21447,10 +21447,10 @@
         <v>955.2</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="14" t="n">
         <v>140</v>
@@ -21550,10 +21550,10 @@
         <v>453</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="14" t="n">
         <v>35.27</v>
@@ -21653,10 +21653,10 @@
         <v>1456.8</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="14" t="n">
         <v>47.93</v>
@@ -21756,10 +21756,10 @@
         <v>7157.4</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="14" t="n">
         <v>511.39</v>
@@ -21859,10 +21859,10 @@
         <v>4069.8</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="14" t="n">
         <v>113.38</v>
@@ -21962,10 +21962,10 @@
         <v>492</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="14" t="n">
         <v>0</v>
@@ -22065,10 +22065,10 @@
         <v>2148.6</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="14" t="n">
         <v>26.94</v>
@@ -22168,10 +22168,10 @@
         <v>3624.6</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="14" t="n">
         <v>44.52</v>
@@ -22271,10 +22271,10 @@
         <v>2377.2</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="14" t="n">
         <v>42.6</v>
@@ -22374,10 +22374,10 @@
         <v>3589.8</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="14" t="n">
         <v>42.94</v>
@@ -22477,10 +22477,10 @@
         <v>229.8</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="14" t="n">
         <v>26.52</v>
@@ -22580,10 +22580,10 @@
         <v>630.6</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="14" t="n">
         <v>38.7</v>
@@ -22683,10 +22683,10 @@
         <v>38.4</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="14" t="n">
         <v>0</v>
@@ -22786,10 +22786,10 @@
         <v>11.4</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="14" t="n">
         <v>0</v>
@@ -22889,10 +22889,10 @@
         <v>106.8</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="14" t="n">
         <v>0</v>
@@ -22992,10 +22992,10 @@
         <v>556.8</v>
       </c>
       <c r="K69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="14" t="n">
         <v>0</v>
@@ -23095,10 +23095,10 @@
         <v>206.4</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="14" t="n">
         <v>0</v>
@@ -23198,10 +23198,10 @@
         <v>3802.2</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="14" t="n">
         <v>308.26</v>
@@ -23301,10 +23301,10 @@
         <v>3993.6</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="14" t="n">
         <v>547.74</v>
@@ -23404,10 +23404,10 @@
         <v>12469.2</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="14" t="n">
         <v>432.22</v>
@@ -23507,10 +23507,10 @@
         <v>3237</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="14" t="n">
         <v>200.26</v>
@@ -23610,10 +23610,10 @@
         <v>6800.4</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="14" t="n">
         <v>234.08</v>
@@ -23713,10 +23713,10 @@
         <v>2521.8</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="14" t="n">
         <v>397.13</v>
@@ -23816,10 +23816,10 @@
         <v>15269.4</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="14" t="n">
         <v>1036.45</v>
@@ -23919,10 +23919,10 @@
         <v>934.8</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="14" t="n">
         <v>620.65</v>
@@ -24022,10 +24022,10 @@
         <v>13779</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="14" t="n">
         <v>449.79</v>
@@ -24125,10 +24125,10 @@
         <v>387</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="14" t="n">
         <v>55.94</v>
@@ -24228,10 +24228,10 @@
         <v>12882</v>
       </c>
       <c r="K81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="14" t="n">
         <v>526.1799999999999</v>
@@ -24331,10 +24331,10 @@
         <v>9390</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>922.6799999999999</v>
@@ -24434,10 +24434,10 @@
         <v>16966.8</v>
       </c>
       <c r="K83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="14" t="n">
         <v>1108.89</v>
@@ -24537,10 +24537,10 @@
         <v>6364.2</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>0</v>
@@ -24640,10 +24640,10 @@
         <v>3172.2</v>
       </c>
       <c r="K85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="14" t="n">
         <v>319.2</v>
@@ -24743,10 +24743,10 @@
         <v>5683.2</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="14" t="n">
         <v>553.05</v>
@@ -24846,10 +24846,10 @@
         <v>8480.4</v>
       </c>
       <c r="K87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="14" t="n">
         <v>580.16</v>
@@ -24949,10 +24949,10 @@
         <v>5442.6</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="14" t="n">
         <v>612.7</v>
@@ -25052,10 +25052,10 @@
         <v>2920.2</v>
       </c>
       <c r="K89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="14" t="n">
         <v>417.76</v>
@@ -25155,10 +25155,10 @@
         <v>27458.4</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="14" t="n">
         <v>971.04</v>
@@ -25258,10 +25258,10 @@
         <v>14328.6</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="14" t="n">
         <v>716.8</v>
@@ -25361,10 +25361,10 @@
         <v>574.2</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>199.31</v>
@@ -25464,10 +25464,10 @@
         <v>9565.799999999999</v>
       </c>
       <c r="K93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="14" t="n">
         <v>281.28</v>
@@ -25567,10 +25567,10 @@
         <v>3690</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>441.5</v>
@@ -25670,10 +25670,10 @@
         <v>7170.6</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="14" t="n">
         <v>449.79</v>
@@ -25773,10 +25773,10 @@
         <v>5788.8</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="14" t="n">
         <v>295.77</v>
@@ -25876,10 +25876,10 @@
         <v>2700.6</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="14" t="n">
         <v>86.18000000000001</v>
@@ -25979,10 +25979,10 @@
         <v>6644.4</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="14" t="n">
         <v>275.22</v>
@@ -26082,10 +26082,10 @@
         <v>1964.4</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="14" t="n">
         <v>300.38</v>
@@ -26185,10 +26185,10 @@
         <v>1474.2</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="14" t="n">
         <v>128.8</v>
@@ -26288,10 +26288,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="14" t="n">
         <v>16.31</v>
@@ -26391,10 +26391,10 @@
         <v>3078</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>517.33</v>
@@ -26494,10 +26494,10 @@
         <v>162.6</v>
       </c>
       <c r="K103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="14" t="n">
         <v>26.88</v>
@@ -26597,10 +26597,10 @@
         <v>10652.4</v>
       </c>
       <c r="K104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="14" t="n">
         <v>456.4</v>
@@ -26700,10 +26700,10 @@
         <v>3478.8</v>
       </c>
       <c r="K105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="14" t="n">
         <v>409.33</v>
@@ -26803,10 +26803,10 @@
         <v>936.6</v>
       </c>
       <c r="K106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="14" t="n">
         <v>253.79</v>
@@ -26906,10 +26906,10 @@
         <v>2715.6</v>
       </c>
       <c r="K107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="14" t="n">
         <v>0</v>
@@ -27009,10 +27009,10 @@
         <v>1450.8</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="14" t="n">
         <v>57.51</v>
@@ -27112,10 +27112,10 @@
         <v>819</v>
       </c>
       <c r="K109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="14" t="n">
         <v>666.34</v>
@@ -27215,10 +27215,10 @@
         <v>156</v>
       </c>
       <c r="K110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="14" t="n">
         <v>5.19</v>
@@ -27318,10 +27318,10 @@
         <v>3368.4</v>
       </c>
       <c r="K111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="14" t="n">
         <v>514.25</v>
@@ -27421,10 +27421,10 @@
         <v>27196.2</v>
       </c>
       <c r="K112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="14" t="n">
         <v>787.54</v>
@@ -27524,10 +27524,10 @@
         <v>466.8</v>
       </c>
       <c r="K113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="14" t="n">
         <v>57.06</v>
@@ -27627,10 +27627,10 @@
         <v>2098.8</v>
       </c>
       <c r="K114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="14" t="n">
         <v>526.23</v>
@@ -27730,10 +27730,10 @@
         <v>8725.799999999999</v>
       </c>
       <c r="K115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="14" t="n">
         <v>360.42</v>
@@ -27833,10 +27833,10 @@
         <v>61855.8</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="14" t="n">
         <v>1867.91</v>
@@ -27936,10 +27936,10 @@
         <v>227.4</v>
       </c>
       <c r="K117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="14" t="n">
         <v>8.4</v>
@@ -28039,10 +28039,10 @@
         <v>4406.4</v>
       </c>
       <c r="K118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="14" t="n">
         <v>658.5599999999999</v>
@@ -28142,10 +28142,10 @@
         <v>5078.4</v>
       </c>
       <c r="K119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="14" t="n">
         <v>836.66</v>
@@ -28245,10 +28245,10 @@
         <v>6370.8</v>
       </c>
       <c r="K120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="14" t="n">
         <v>211.06</v>
@@ -28348,10 +28348,10 @@
         <v>2863.8</v>
       </c>
       <c r="K121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="14" t="n">
         <v>120.51</v>
@@ -28451,10 +28451,10 @@
         <v>11926.8</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="14" t="n">
         <v>386.06</v>
@@ -28554,10 +28554,10 @@
         <v>1468.8</v>
       </c>
       <c r="K123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="14" t="n">
         <v>191.06</v>
@@ -28657,10 +28657,10 @@
         <v>9572.4</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="14" t="n">
         <v>609.39</v>
@@ -28760,10 +28760,10 @@
         <v>6314.4</v>
       </c>
       <c r="K125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="14" t="n">
         <v>434.31</v>
@@ -28863,10 +28863,10 @@
         <v>2530.8</v>
       </c>
       <c r="K126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="14" t="n">
         <v>128.58</v>
@@ -28966,10 +28966,10 @@
         <v>3376.8</v>
       </c>
       <c r="K127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="14" t="n">
         <v>415.67</v>
@@ -29069,10 +29069,10 @@
         <v>6669.6</v>
       </c>
       <c r="K128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="14" t="n">
         <v>672.9</v>
@@ -29172,10 +29172,10 @@
         <v>463.2</v>
       </c>
       <c r="K129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="14" t="n">
         <v>289.52</v>
@@ -29275,10 +29275,10 @@
         <v>2230.2</v>
       </c>
       <c r="K130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="14" t="n">
         <v>147.62</v>
@@ -29378,10 +29378,10 @@
         <v>598.2</v>
       </c>
       <c r="K131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="14" t="n">
         <v>24.75</v>
@@ -29481,10 +29481,10 @@
         <v>2652.6</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="14" t="n">
         <v>95.42</v>
@@ -29584,10 +29584,10 @@
         <v>790.2</v>
       </c>
       <c r="K133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="14" t="n">
         <v>448.56</v>
@@ -29687,10 +29687,10 @@
         <v>13406.4</v>
       </c>
       <c r="K134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="14" t="n">
         <v>504.31</v>
@@ -29790,10 +29790,10 @@
         <v>8152.8</v>
       </c>
       <c r="K135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="14" t="n">
         <v>313.04</v>
@@ -29893,10 +29893,10 @@
         <v>1092</v>
       </c>
       <c r="K136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="14" t="n">
         <v>23.5</v>
@@ -29996,10 +29996,10 @@
         <v>1350</v>
       </c>
       <c r="K137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="14" t="n">
         <v>17.2</v>
@@ -30099,10 +30099,10 @@
         <v>2592</v>
       </c>
       <c r="K138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>45.2</v>
@@ -30202,10 +30202,10 @@
         <v>1344</v>
       </c>
       <c r="K139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="14" t="n">
         <v>11.8</v>
@@ -30305,10 +30305,10 @@
         <v>2112</v>
       </c>
       <c r="K140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>23.5</v>
@@ -30408,10 +30408,10 @@
         <v>522</v>
       </c>
       <c r="K141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="14" t="n">
         <v>3.6</v>
@@ -30511,10 +30511,10 @@
         <v>948</v>
       </c>
       <c r="K142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="14" t="n">
         <v>6.7</v>
@@ -30614,10 +30614,10 @@
         <v>1698</v>
       </c>
       <c r="K143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="14" t="n">
         <v>15.2</v>
@@ -30717,10 +30717,10 @@
         <v>1344</v>
       </c>
       <c r="K144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="14" t="n">
         <v>13.5</v>
@@ -30820,10 +30820,10 @@
         <v>912</v>
       </c>
       <c r="K145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" s="14" t="n">
         <v>15.6</v>
@@ -31794,10 +31794,10 @@
         <v>7290</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>894.24</v>
@@ -31897,10 +31897,10 @@
         <v>4104</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="14" t="n">
         <v>170.58</v>
@@ -32000,10 +32000,10 @@
         <v>648</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>132.16</v>
@@ -32103,10 +32103,10 @@
         <v>2691.6</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="14" t="n">
         <v>98.78</v>
@@ -32206,10 +32206,10 @@
         <v>4605.6</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="14" t="n">
         <v>213.19</v>
@@ -32309,10 +32309,10 @@
         <v>3080.4</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="14" t="n">
         <v>392.6</v>
@@ -32412,10 +32412,10 @@
         <v>2517</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="14" t="n">
         <v>99.29000000000001</v>
@@ -32515,10 +32515,10 @@
         <v>4983</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="14" t="n">
         <v>213.81</v>
@@ -32618,10 +32618,10 @@
         <v>1086</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>51.91</v>
@@ -32721,10 +32721,10 @@
         <v>10640.4</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="14" t="n">
         <v>379.74</v>
@@ -32824,10 +32824,10 @@
         <v>3801</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="14" t="n">
         <v>145.6</v>
@@ -32927,10 +32927,10 @@
         <v>1252.2</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="14" t="n">
         <v>278.82</v>
@@ -33030,10 +33030,10 @@
         <v>211.2</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="14" t="n">
         <v>12.32</v>
@@ -33133,10 +33133,10 @@
         <v>462</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="14" t="n">
         <v>28.06</v>
@@ -33236,10 +33236,10 @@
         <v>3237</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="14" t="n">
         <v>94.69</v>
@@ -33339,10 +33339,10 @@
         <v>1746.6</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="14" t="n">
         <v>241.92</v>
@@ -33442,10 +33442,10 @@
         <v>14563.8</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>512.1799999999999</v>
@@ -33545,10 +33545,10 @@
         <v>2434.2</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="14" t="n">
         <v>712.98</v>
@@ -33648,10 +33648,10 @@
         <v>1863</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="14" t="n">
         <v>299.88</v>
@@ -33751,10 +33751,10 @@
         <v>159.6</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="14" t="n">
         <v>14.39</v>
@@ -33854,10 +33854,10 @@
         <v>1160.4</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>41.47</v>
@@ -33957,10 +33957,10 @@
         <v>708</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>21.08</v>
@@ -34060,10 +34060,10 @@
         <v>389.4</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="14" t="n">
         <v>23.04</v>
@@ -34163,10 +34163,10 @@
         <v>726.6</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="14" t="n">
         <v>16.9</v>
@@ -34266,10 +34266,10 @@
         <v>8652</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>297.77</v>
@@ -34369,10 +34369,10 @@
         <v>4332.6</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="14" t="n">
         <v>333.2</v>
@@ -34472,10 +34472,10 @@
         <v>2785.8</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="14" t="n">
         <v>135.52</v>
@@ -34575,10 +34575,10 @@
         <v>3174</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="14" t="n">
         <v>645.5700000000001</v>
@@ -34678,10 +34678,10 @@
         <v>1678.2</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="14" t="n">
         <v>42.94</v>
@@ -34781,10 +34781,10 @@
         <v>2715</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="14" t="n">
         <v>42.81</v>
@@ -34884,10 +34884,10 @@
         <v>3547.8</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="14" t="n">
         <v>60.32</v>
@@ -34987,10 +34987,10 @@
         <v>121.2</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="14" t="n">
         <v>0</v>
@@ -35090,10 +35090,10 @@
         <v>1218.6</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="14" t="n">
         <v>107.02</v>
@@ -35193,10 +35193,10 @@
         <v>8877.6</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="14" t="n">
         <v>482.16</v>
@@ -35296,10 +35296,10 @@
         <v>3243</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="14" t="n">
         <v>252</v>
@@ -35399,10 +35399,10 @@
         <v>640.8</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="14" t="n">
         <v>0</v>
@@ -35502,10 +35502,10 @@
         <v>1182</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="14" t="n">
         <v>0</v>
@@ -35605,10 +35605,10 @@
         <v>8056.8</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="14" t="n">
         <v>211.33</v>
@@ -35708,10 +35708,10 @@
         <v>1378.2</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="14" t="n">
         <v>94.08</v>
@@ -35811,10 +35811,10 @@
         <v>8125.8</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="14" t="n">
         <v>996.76</v>
@@ -35914,10 +35914,10 @@
         <v>403.2</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="14" t="n">
         <v>29.4</v>
@@ -36017,10 +36017,10 @@
         <v>426</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="14" t="n">
         <v>31.95</v>
@@ -36120,10 +36120,10 @@
         <v>3160.2</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="14" t="n">
         <v>346.47</v>
@@ -36223,10 +36223,10 @@
         <v>1113</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="14" t="n">
         <v>53.04</v>
@@ -36326,10 +36326,10 @@
         <v>831</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="14" t="n">
         <v>31.95</v>
@@ -36429,10 +36429,10 @@
         <v>1872</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="14" t="n">
         <v>36.1</v>
@@ -36532,10 +36532,10 @@
         <v>955.2</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="14" t="n">
         <v>140</v>
@@ -36635,10 +36635,10 @@
         <v>453</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="14" t="n">
         <v>35.27</v>
@@ -36738,10 +36738,10 @@
         <v>1456.8</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="14" t="n">
         <v>47.93</v>
@@ -36841,10 +36841,10 @@
         <v>7157.4</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="14" t="n">
         <v>511.39</v>
@@ -36944,10 +36944,10 @@
         <v>4069.8</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="14" t="n">
         <v>113.38</v>
@@ -37047,10 +37047,10 @@
         <v>492</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="14" t="n">
         <v>0</v>
@@ -37150,10 +37150,10 @@
         <v>2148.6</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="14" t="n">
         <v>26.94</v>
@@ -37253,10 +37253,10 @@
         <v>3624.6</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="14" t="n">
         <v>44.52</v>
@@ -37356,10 +37356,10 @@
         <v>2377.2</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="14" t="n">
         <v>42.6</v>
@@ -37459,10 +37459,10 @@
         <v>3589.8</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="14" t="n">
         <v>42.94</v>
@@ -37562,10 +37562,10 @@
         <v>229.8</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="14" t="n">
         <v>26.52</v>
@@ -37665,10 +37665,10 @@
         <v>630.6</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="14" t="n">
         <v>38.7</v>
@@ -37768,10 +37768,10 @@
         <v>38.4</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="14" t="n">
         <v>0</v>
@@ -37871,10 +37871,10 @@
         <v>11.4</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="14" t="n">
         <v>0</v>
@@ -37974,10 +37974,10 @@
         <v>106.8</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="14" t="n">
         <v>0</v>
@@ -38077,10 +38077,10 @@
         <v>556.8</v>
       </c>
       <c r="K69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="14" t="n">
         <v>0</v>
@@ -38180,10 +38180,10 @@
         <v>206.4</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="14" t="n">
         <v>0</v>
@@ -38283,10 +38283,10 @@
         <v>3802.2</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="14" t="n">
         <v>308.26</v>
@@ -38386,10 +38386,10 @@
         <v>3993.6</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="14" t="n">
         <v>547.74</v>
@@ -38489,10 +38489,10 @@
         <v>12469.2</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="14" t="n">
         <v>432.22</v>
@@ -38592,10 +38592,10 @@
         <v>3237</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="14" t="n">
         <v>200.26</v>
@@ -38695,10 +38695,10 @@
         <v>6800.4</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="14" t="n">
         <v>234.08</v>
@@ -38798,10 +38798,10 @@
         <v>2521.8</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="14" t="n">
         <v>397.13</v>
@@ -38901,10 +38901,10 @@
         <v>15269.4</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="14" t="n">
         <v>1036.45</v>
@@ -39004,10 +39004,10 @@
         <v>934.8</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="14" t="n">
         <v>620.65</v>
@@ -39107,10 +39107,10 @@
         <v>13779</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="14" t="n">
         <v>449.79</v>
@@ -39210,10 +39210,10 @@
         <v>387</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="14" t="n">
         <v>55.94</v>
@@ -39313,10 +39313,10 @@
         <v>12882</v>
       </c>
       <c r="K81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="14" t="n">
         <v>526.1799999999999</v>
@@ -39416,10 +39416,10 @@
         <v>9390</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>922.6799999999999</v>
@@ -39519,10 +39519,10 @@
         <v>16966.8</v>
       </c>
       <c r="K83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="14" t="n">
         <v>1108.89</v>
@@ -39622,10 +39622,10 @@
         <v>6364.2</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>0</v>
@@ -39725,10 +39725,10 @@
         <v>3172.2</v>
       </c>
       <c r="K85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="14" t="n">
         <v>319.2</v>
@@ -39828,10 +39828,10 @@
         <v>5683.2</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="14" t="n">
         <v>553.05</v>
@@ -39931,10 +39931,10 @@
         <v>8480.4</v>
       </c>
       <c r="K87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="14" t="n">
         <v>580.16</v>
@@ -40034,10 +40034,10 @@
         <v>5442.6</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="14" t="n">
         <v>612.7</v>
@@ -40137,10 +40137,10 @@
         <v>2920.2</v>
       </c>
       <c r="K89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="14" t="n">
         <v>417.76</v>
@@ -40240,10 +40240,10 @@
         <v>27458.4</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="14" t="n">
         <v>971.04</v>
@@ -40343,10 +40343,10 @@
         <v>14328.6</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="14" t="n">
         <v>716.8</v>
@@ -40446,10 +40446,10 @@
         <v>574.2</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>199.31</v>
@@ -40549,10 +40549,10 @@
         <v>9565.799999999999</v>
       </c>
       <c r="K93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="14" t="n">
         <v>281.28</v>
@@ -40652,10 +40652,10 @@
         <v>3690</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>441.5</v>
@@ -40755,10 +40755,10 @@
         <v>7170.6</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="14" t="n">
         <v>449.79</v>
@@ -40858,10 +40858,10 @@
         <v>5788.8</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="14" t="n">
         <v>295.77</v>
@@ -40961,10 +40961,10 @@
         <v>2700.6</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="14" t="n">
         <v>86.18000000000001</v>
@@ -41064,10 +41064,10 @@
         <v>6644.4</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="14" t="n">
         <v>275.22</v>
@@ -41167,10 +41167,10 @@
         <v>1964.4</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="14" t="n">
         <v>300.38</v>
@@ -41270,10 +41270,10 @@
         <v>1474.2</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="14" t="n">
         <v>128.8</v>
@@ -41373,10 +41373,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="14" t="n">
         <v>16.31</v>
@@ -41476,10 +41476,10 @@
         <v>3078</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>517.33</v>
@@ -41579,10 +41579,10 @@
         <v>162.6</v>
       </c>
       <c r="K103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="14" t="n">
         <v>26.88</v>
@@ -41682,10 +41682,10 @@
         <v>10652.4</v>
       </c>
       <c r="K104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="14" t="n">
         <v>456.4</v>
@@ -41785,10 +41785,10 @@
         <v>3478.8</v>
       </c>
       <c r="K105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="14" t="n">
         <v>409.33</v>
@@ -41888,10 +41888,10 @@
         <v>936.6</v>
       </c>
       <c r="K106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="14" t="n">
         <v>253.79</v>
@@ -41991,10 +41991,10 @@
         <v>2715.6</v>
       </c>
       <c r="K107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="14" t="n">
         <v>0</v>
@@ -42094,10 +42094,10 @@
         <v>1450.8</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="14" t="n">
         <v>57.51</v>
@@ -42197,10 +42197,10 @@
         <v>819</v>
       </c>
       <c r="K109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="14" t="n">
         <v>666.34</v>
@@ -42300,10 +42300,10 @@
         <v>156</v>
       </c>
       <c r="K110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="14" t="n">
         <v>5.19</v>
@@ -42403,10 +42403,10 @@
         <v>3368.4</v>
       </c>
       <c r="K111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="14" t="n">
         <v>514.25</v>
@@ -42506,10 +42506,10 @@
         <v>27196.2</v>
       </c>
       <c r="K112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="14" t="n">
         <v>787.54</v>
@@ -42609,10 +42609,10 @@
         <v>466.8</v>
       </c>
       <c r="K113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="14" t="n">
         <v>57.06</v>
@@ -42712,10 +42712,10 @@
         <v>2098.8</v>
       </c>
       <c r="K114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="14" t="n">
         <v>526.23</v>
@@ -42815,10 +42815,10 @@
         <v>8725.799999999999</v>
       </c>
       <c r="K115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="14" t="n">
         <v>360.42</v>
@@ -42918,10 +42918,10 @@
         <v>61855.8</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="14" t="n">
         <v>1867.91</v>
@@ -43021,10 +43021,10 @@
         <v>227.4</v>
       </c>
       <c r="K117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="14" t="n">
         <v>8.4</v>
@@ -43124,10 +43124,10 @@
         <v>4406.4</v>
       </c>
       <c r="K118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="14" t="n">
         <v>658.5599999999999</v>
@@ -43227,10 +43227,10 @@
         <v>5078.4</v>
       </c>
       <c r="K119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="14" t="n">
         <v>836.66</v>
@@ -43330,10 +43330,10 @@
         <v>6370.8</v>
       </c>
       <c r="K120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="14" t="n">
         <v>211.06</v>
@@ -43433,10 +43433,10 @@
         <v>2863.8</v>
       </c>
       <c r="K121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="14" t="n">
         <v>120.51</v>
@@ -43536,10 +43536,10 @@
         <v>11926.8</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="14" t="n">
         <v>386.06</v>
@@ -43639,10 +43639,10 @@
         <v>1468.8</v>
       </c>
       <c r="K123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="14" t="n">
         <v>191.06</v>
@@ -43742,10 +43742,10 @@
         <v>9572.4</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="14" t="n">
         <v>609.39</v>
@@ -43845,10 +43845,10 @@
         <v>6314.4</v>
       </c>
       <c r="K125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="14" t="n">
         <v>434.31</v>
@@ -43948,10 +43948,10 @@
         <v>2530.8</v>
       </c>
       <c r="K126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="14" t="n">
         <v>128.58</v>
@@ -44051,10 +44051,10 @@
         <v>3376.8</v>
       </c>
       <c r="K127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="14" t="n">
         <v>415.67</v>
@@ -44154,10 +44154,10 @@
         <v>6669.6</v>
       </c>
       <c r="K128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="14" t="n">
         <v>672.9</v>
@@ -44257,10 +44257,10 @@
         <v>463.2</v>
       </c>
       <c r="K129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="14" t="n">
         <v>289.52</v>
@@ -44360,10 +44360,10 @@
         <v>2230.2</v>
       </c>
       <c r="K130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="14" t="n">
         <v>147.62</v>
@@ -44463,10 +44463,10 @@
         <v>598.2</v>
       </c>
       <c r="K131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="14" t="n">
         <v>24.75</v>
@@ -44566,10 +44566,10 @@
         <v>2652.6</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="14" t="n">
         <v>95.42</v>
@@ -44669,10 +44669,10 @@
         <v>790.2</v>
       </c>
       <c r="K133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="14" t="n">
         <v>448.56</v>
@@ -44772,10 +44772,10 @@
         <v>13406.4</v>
       </c>
       <c r="K134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="14" t="n">
         <v>504.31</v>
@@ -44875,10 +44875,10 @@
         <v>8152.8</v>
       </c>
       <c r="K135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="14" t="n">
         <v>313.04</v>
@@ -44978,10 +44978,10 @@
         <v>1092</v>
       </c>
       <c r="K136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="14" t="n">
         <v>23.5</v>
@@ -45081,10 +45081,10 @@
         <v>1350</v>
       </c>
       <c r="K137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="14" t="n">
         <v>17.2</v>
@@ -45184,10 +45184,10 @@
         <v>2592</v>
       </c>
       <c r="K138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>45.2</v>
@@ -45287,10 +45287,10 @@
         <v>1344</v>
       </c>
       <c r="K139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="14" t="n">
         <v>11.8</v>
@@ -45390,10 +45390,10 @@
         <v>2112</v>
       </c>
       <c r="K140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>23.5</v>
@@ -45493,10 +45493,10 @@
         <v>522</v>
       </c>
       <c r="K141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="14" t="n">
         <v>3.6</v>
@@ -45596,10 +45596,10 @@
         <v>948</v>
       </c>
       <c r="K142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="14" t="n">
         <v>6.7</v>
@@ -45699,10 +45699,10 @@
         <v>1698</v>
       </c>
       <c r="K143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="14" t="n">
         <v>15.2</v>
@@ -45802,10 +45802,10 @@
         <v>1344</v>
       </c>
       <c r="K144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="14" t="n">
         <v>13.5</v>
@@ -45905,10 +45905,10 @@
         <v>912</v>
       </c>
       <c r="K145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" s="14" t="n">
         <v>15.6</v>
@@ -46879,10 +46879,10 @@
         <v>7290</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>894.24</v>
@@ -46982,10 +46982,10 @@
         <v>4104</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="14" t="n">
         <v>170.58</v>
@@ -47085,10 +47085,10 @@
         <v>648</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>132.16</v>
@@ -47188,10 +47188,10 @@
         <v>2691.6</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="14" t="n">
         <v>98.78</v>
@@ -47291,10 +47291,10 @@
         <v>4605.6</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="14" t="n">
         <v>213.19</v>
@@ -47394,10 +47394,10 @@
         <v>3080.4</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="14" t="n">
         <v>392.6</v>
@@ -47497,10 +47497,10 @@
         <v>2517</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="14" t="n">
         <v>99.29000000000001</v>
@@ -47600,10 +47600,10 @@
         <v>4983</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="14" t="n">
         <v>213.81</v>
@@ -47703,10 +47703,10 @@
         <v>1086</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>51.91</v>
@@ -47806,10 +47806,10 @@
         <v>10640.4</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="14" t="n">
         <v>379.74</v>
@@ -47909,10 +47909,10 @@
         <v>3801</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="14" t="n">
         <v>145.6</v>
@@ -48012,10 +48012,10 @@
         <v>1252.2</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="14" t="n">
         <v>278.82</v>
@@ -48115,10 +48115,10 @@
         <v>211.2</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="14" t="n">
         <v>12.32</v>
@@ -48218,10 +48218,10 @@
         <v>462</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="14" t="n">
         <v>28.06</v>
@@ -48321,10 +48321,10 @@
         <v>3237</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="14" t="n">
         <v>94.69</v>
@@ -48424,10 +48424,10 @@
         <v>1746.6</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="14" t="n">
         <v>241.92</v>
@@ -48527,10 +48527,10 @@
         <v>14563.8</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>512.1799999999999</v>
@@ -48630,10 +48630,10 @@
         <v>2434.2</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="14" t="n">
         <v>712.98</v>
@@ -48733,10 +48733,10 @@
         <v>1863</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="14" t="n">
         <v>299.88</v>
@@ -48836,10 +48836,10 @@
         <v>159.6</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="14" t="n">
         <v>14.39</v>
@@ -48939,10 +48939,10 @@
         <v>1160.4</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>41.47</v>
@@ -49042,10 +49042,10 @@
         <v>708</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>21.08</v>
@@ -49145,10 +49145,10 @@
         <v>389.4</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="14" t="n">
         <v>23.04</v>
@@ -49248,10 +49248,10 @@
         <v>726.6</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="14" t="n">
         <v>16.9</v>
@@ -49351,10 +49351,10 @@
         <v>8652</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>297.77</v>
@@ -49454,10 +49454,10 @@
         <v>4332.6</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="14" t="n">
         <v>333.2</v>
@@ -49557,10 +49557,10 @@
         <v>2785.8</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="14" t="n">
         <v>135.52</v>
@@ -49660,10 +49660,10 @@
         <v>3174</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="14" t="n">
         <v>645.5700000000001</v>
@@ -49763,10 +49763,10 @@
         <v>1678.2</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="14" t="n">
         <v>42.94</v>
@@ -49866,10 +49866,10 @@
         <v>2715</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="14" t="n">
         <v>42.81</v>
@@ -49969,10 +49969,10 @@
         <v>3547.8</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="14" t="n">
         <v>60.32</v>
@@ -50072,10 +50072,10 @@
         <v>121.2</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="14" t="n">
         <v>0</v>
@@ -50175,10 +50175,10 @@
         <v>1218.6</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="14" t="n">
         <v>107.02</v>
@@ -50278,10 +50278,10 @@
         <v>8877.6</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="14" t="n">
         <v>482.16</v>
@@ -50381,10 +50381,10 @@
         <v>3243</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="14" t="n">
         <v>252</v>
@@ -50484,10 +50484,10 @@
         <v>640.8</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="14" t="n">
         <v>0</v>
@@ -50587,10 +50587,10 @@
         <v>1182</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="14" t="n">
         <v>0</v>
@@ -50690,10 +50690,10 @@
         <v>8056.8</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="14" t="n">
         <v>211.33</v>
@@ -50793,10 +50793,10 @@
         <v>1378.2</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="14" t="n">
         <v>94.08</v>
@@ -50896,10 +50896,10 @@
         <v>8125.8</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="14" t="n">
         <v>996.76</v>
@@ -50999,10 +50999,10 @@
         <v>403.2</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="14" t="n">
         <v>29.4</v>
@@ -51102,10 +51102,10 @@
         <v>426</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="14" t="n">
         <v>31.95</v>
@@ -51205,10 +51205,10 @@
         <v>3160.2</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="14" t="n">
         <v>346.47</v>
@@ -51308,10 +51308,10 @@
         <v>1113</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="14" t="n">
         <v>53.04</v>
@@ -51411,10 +51411,10 @@
         <v>831</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="14" t="n">
         <v>31.95</v>
@@ -51514,10 +51514,10 @@
         <v>1872</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="14" t="n">
         <v>36.1</v>
@@ -51617,10 +51617,10 @@
         <v>955.2</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="14" t="n">
         <v>140</v>
@@ -51720,10 +51720,10 @@
         <v>453</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="14" t="n">
         <v>35.27</v>
@@ -51823,10 +51823,10 @@
         <v>1456.8</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="14" t="n">
         <v>47.93</v>
@@ -51926,10 +51926,10 @@
         <v>7157.4</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="14" t="n">
         <v>511.39</v>
@@ -52029,10 +52029,10 @@
         <v>4069.8</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="14" t="n">
         <v>113.38</v>
@@ -52132,10 +52132,10 @@
         <v>492</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="14" t="n">
         <v>0</v>
@@ -52235,10 +52235,10 @@
         <v>2148.6</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="14" t="n">
         <v>26.94</v>
@@ -52338,10 +52338,10 @@
         <v>3624.6</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="14" t="n">
         <v>44.52</v>
@@ -52441,10 +52441,10 @@
         <v>2377.2</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="14" t="n">
         <v>42.6</v>
@@ -52544,10 +52544,10 @@
         <v>3589.8</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="14" t="n">
         <v>42.94</v>
@@ -52647,10 +52647,10 @@
         <v>229.8</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="14" t="n">
         <v>26.52</v>
@@ -52750,10 +52750,10 @@
         <v>630.6</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="14" t="n">
         <v>38.7</v>
@@ -52853,10 +52853,10 @@
         <v>38.4</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="14" t="n">
         <v>0</v>
@@ -52956,10 +52956,10 @@
         <v>11.4</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="14" t="n">
         <v>0</v>
@@ -53059,10 +53059,10 @@
         <v>106.8</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="14" t="n">
         <v>0</v>
@@ -53162,10 +53162,10 @@
         <v>556.8</v>
       </c>
       <c r="K69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="14" t="n">
         <v>0</v>
@@ -53265,10 +53265,10 @@
         <v>206.4</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="14" t="n">
         <v>0</v>
@@ -53368,10 +53368,10 @@
         <v>3802.2</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="14" t="n">
         <v>308.26</v>
@@ -53471,10 +53471,10 @@
         <v>3993.6</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="14" t="n">
         <v>547.74</v>
@@ -53574,10 +53574,10 @@
         <v>12469.2</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="14" t="n">
         <v>432.22</v>
@@ -53677,10 +53677,10 @@
         <v>3237</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="14" t="n">
         <v>200.26</v>
@@ -53780,10 +53780,10 @@
         <v>6800.4</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="14" t="n">
         <v>234.08</v>
@@ -53883,10 +53883,10 @@
         <v>2521.8</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="14" t="n">
         <v>397.13</v>
@@ -53986,10 +53986,10 @@
         <v>15269.4</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="14" t="n">
         <v>1036.45</v>
@@ -54089,10 +54089,10 @@
         <v>934.8</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="14" t="n">
         <v>620.65</v>
@@ -54192,10 +54192,10 @@
         <v>13779</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="14" t="n">
         <v>449.79</v>
@@ -54295,10 +54295,10 @@
         <v>387</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="14" t="n">
         <v>55.94</v>
@@ -54398,10 +54398,10 @@
         <v>12882</v>
       </c>
       <c r="K81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="14" t="n">
         <v>526.1799999999999</v>
@@ -54501,10 +54501,10 @@
         <v>9390</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>922.6799999999999</v>
@@ -54604,10 +54604,10 @@
         <v>16966.8</v>
       </c>
       <c r="K83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="14" t="n">
         <v>1108.89</v>
@@ -54707,10 +54707,10 @@
         <v>6364.2</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>0</v>
@@ -54810,10 +54810,10 @@
         <v>3172.2</v>
       </c>
       <c r="K85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="14" t="n">
         <v>319.2</v>
@@ -54913,10 +54913,10 @@
         <v>5683.2</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="14" t="n">
         <v>553.05</v>
@@ -55016,10 +55016,10 @@
         <v>8480.4</v>
       </c>
       <c r="K87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="14" t="n">
         <v>580.16</v>
@@ -55119,10 +55119,10 @@
         <v>5442.6</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="14" t="n">
         <v>612.7</v>
@@ -55222,10 +55222,10 @@
         <v>2920.2</v>
       </c>
       <c r="K89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="14" t="n">
         <v>417.76</v>
@@ -55325,10 +55325,10 @@
         <v>27458.4</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="14" t="n">
         <v>971.04</v>
@@ -55428,10 +55428,10 @@
         <v>14328.6</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="14" t="n">
         <v>716.8</v>
@@ -55531,10 +55531,10 @@
         <v>574.2</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>199.31</v>
@@ -55634,10 +55634,10 @@
         <v>9565.799999999999</v>
       </c>
       <c r="K93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="14" t="n">
         <v>281.28</v>
@@ -55737,10 +55737,10 @@
         <v>3690</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>441.5</v>
@@ -55840,10 +55840,10 @@
         <v>7170.6</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="14" t="n">
         <v>449.79</v>
@@ -55943,10 +55943,10 @@
         <v>5788.8</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="14" t="n">
         <v>295.77</v>
@@ -56046,10 +56046,10 @@
         <v>2700.6</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="14" t="n">
         <v>86.18000000000001</v>
@@ -56149,10 +56149,10 @@
         <v>6644.4</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="14" t="n">
         <v>275.22</v>
@@ -56252,10 +56252,10 @@
         <v>1964.4</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="14" t="n">
         <v>300.38</v>
@@ -56355,10 +56355,10 @@
         <v>1474.2</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="14" t="n">
         <v>128.8</v>
@@ -56458,10 +56458,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="14" t="n">
         <v>16.31</v>
@@ -56561,10 +56561,10 @@
         <v>3078</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>517.33</v>
@@ -56664,10 +56664,10 @@
         <v>162.6</v>
       </c>
       <c r="K103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="14" t="n">
         <v>26.88</v>
@@ -56767,10 +56767,10 @@
         <v>10652.4</v>
       </c>
       <c r="K104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="14" t="n">
         <v>456.4</v>
@@ -56870,10 +56870,10 @@
         <v>3478.8</v>
       </c>
       <c r="K105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="14" t="n">
         <v>409.33</v>
@@ -56973,10 +56973,10 @@
         <v>936.6</v>
       </c>
       <c r="K106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="14" t="n">
         <v>253.79</v>
@@ -57076,10 +57076,10 @@
         <v>2715.6</v>
       </c>
       <c r="K107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="14" t="n">
         <v>0</v>
@@ -57179,10 +57179,10 @@
         <v>1450.8</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="14" t="n">
         <v>57.51</v>
@@ -57282,10 +57282,10 @@
         <v>819</v>
       </c>
       <c r="K109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="14" t="n">
         <v>666.34</v>
@@ -57385,10 +57385,10 @@
         <v>156</v>
       </c>
       <c r="K110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="14" t="n">
         <v>5.19</v>
@@ -57488,10 +57488,10 @@
         <v>3368.4</v>
       </c>
       <c r="K111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="14" t="n">
         <v>514.25</v>
@@ -57591,10 +57591,10 @@
         <v>27196.2</v>
       </c>
       <c r="K112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="14" t="n">
         <v>787.54</v>
@@ -57694,10 +57694,10 @@
         <v>466.8</v>
       </c>
       <c r="K113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="14" t="n">
         <v>57.06</v>
@@ -57797,10 +57797,10 @@
         <v>2098.8</v>
       </c>
       <c r="K114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="14" t="n">
         <v>526.23</v>
@@ -57900,10 +57900,10 @@
         <v>8725.799999999999</v>
       </c>
       <c r="K115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="14" t="n">
         <v>360.42</v>
@@ -58003,10 +58003,10 @@
         <v>61855.8</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="14" t="n">
         <v>1867.91</v>
@@ -58106,10 +58106,10 @@
         <v>227.4</v>
       </c>
       <c r="K117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="14" t="n">
         <v>8.4</v>
@@ -58209,10 +58209,10 @@
         <v>4406.4</v>
       </c>
       <c r="K118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="14" t="n">
         <v>658.5599999999999</v>
@@ -58312,10 +58312,10 @@
         <v>5078.4</v>
       </c>
       <c r="K119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="14" t="n">
         <v>836.66</v>
@@ -58415,10 +58415,10 @@
         <v>6370.8</v>
       </c>
       <c r="K120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="14" t="n">
         <v>211.06</v>
@@ -58518,10 +58518,10 @@
         <v>2863.8</v>
       </c>
       <c r="K121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="14" t="n">
         <v>120.51</v>
@@ -58621,10 +58621,10 @@
         <v>11926.8</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="14" t="n">
         <v>386.06</v>
@@ -58724,10 +58724,10 @@
         <v>1468.8</v>
       </c>
       <c r="K123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="14" t="n">
         <v>191.06</v>
@@ -58827,10 +58827,10 @@
         <v>9572.4</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="14" t="n">
         <v>609.39</v>
@@ -58930,10 +58930,10 @@
         <v>6314.4</v>
       </c>
       <c r="K125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="14" t="n">
         <v>434.31</v>
@@ -59033,10 +59033,10 @@
         <v>2530.8</v>
       </c>
       <c r="K126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="14" t="n">
         <v>128.58</v>
@@ -59136,10 +59136,10 @@
         <v>3376.8</v>
       </c>
       <c r="K127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="14" t="n">
         <v>415.67</v>
@@ -59239,10 +59239,10 @@
         <v>6669.6</v>
       </c>
       <c r="K128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="14" t="n">
         <v>672.9</v>
@@ -59342,10 +59342,10 @@
         <v>463.2</v>
       </c>
       <c r="K129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="14" t="n">
         <v>289.52</v>
@@ -59445,10 +59445,10 @@
         <v>2230.2</v>
       </c>
       <c r="K130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="14" t="n">
         <v>147.62</v>
@@ -59548,10 +59548,10 @@
         <v>598.2</v>
       </c>
       <c r="K131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="14" t="n">
         <v>24.75</v>
@@ -59651,10 +59651,10 @@
         <v>2652.6</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="14" t="n">
         <v>95.42</v>
@@ -59754,10 +59754,10 @@
         <v>790.2</v>
       </c>
       <c r="K133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="14" t="n">
         <v>448.56</v>
@@ -59857,10 +59857,10 @@
         <v>13406.4</v>
       </c>
       <c r="K134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="14" t="n">
         <v>504.31</v>
@@ -59960,10 +59960,10 @@
         <v>8152.8</v>
       </c>
       <c r="K135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="14" t="n">
         <v>313.04</v>
@@ -60063,10 +60063,10 @@
         <v>1092</v>
       </c>
       <c r="K136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="14" t="n">
         <v>23.5</v>
@@ -60166,10 +60166,10 @@
         <v>1350</v>
       </c>
       <c r="K137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="14" t="n">
         <v>17.2</v>
@@ -60269,10 +60269,10 @@
         <v>2592</v>
       </c>
       <c r="K138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>45.2</v>
@@ -60372,10 +60372,10 @@
         <v>1344</v>
       </c>
       <c r="K139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="14" t="n">
         <v>11.8</v>
@@ -60475,10 +60475,10 @@
         <v>2112</v>
       </c>
       <c r="K140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>23.5</v>
@@ -60578,10 +60578,10 @@
         <v>522</v>
       </c>
       <c r="K141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="14" t="n">
         <v>3.6</v>
@@ -60681,10 +60681,10 @@
         <v>948</v>
       </c>
       <c r="K142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="14" t="n">
         <v>6.7</v>
@@ -60784,10 +60784,10 @@
         <v>1698</v>
       </c>
       <c r="K143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="14" t="n">
         <v>15.2</v>
@@ -60887,10 +60887,10 @@
         <v>1344</v>
       </c>
       <c r="K144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="14" t="n">
         <v>13.5</v>
@@ -60990,10 +60990,10 @@
         <v>912</v>
       </c>
       <c r="K145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" s="14" t="n">
         <v>15.6</v>
@@ -61964,10 +61964,10 @@
         <v>7290</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="14" t="n">
         <v>894.24</v>
@@ -62067,10 +62067,10 @@
         <v>4104</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="14" t="n">
         <v>170.58</v>
@@ -62170,10 +62170,10 @@
         <v>648</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="14" t="n">
         <v>132.16</v>
@@ -62273,10 +62273,10 @@
         <v>2691.6</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="14" t="n">
         <v>98.78</v>
@@ -62376,10 +62376,10 @@
         <v>4605.6</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="14" t="n">
         <v>213.19</v>
@@ -62479,10 +62479,10 @@
         <v>3080.4</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="14" t="n">
         <v>392.6</v>
@@ -62582,10 +62582,10 @@
         <v>2517</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="14" t="n">
         <v>99.29000000000001</v>
@@ -62685,10 +62685,10 @@
         <v>4983</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="14" t="n">
         <v>213.81</v>
@@ -62788,10 +62788,10 @@
         <v>1086</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="14" t="n">
         <v>51.91</v>
@@ -62891,10 +62891,10 @@
         <v>10640.4</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="14" t="n">
         <v>379.74</v>
@@ -62994,10 +62994,10 @@
         <v>3801</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="14" t="n">
         <v>145.6</v>
@@ -63097,10 +63097,10 @@
         <v>1252.2</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="14" t="n">
         <v>278.82</v>
@@ -63200,10 +63200,10 @@
         <v>211.2</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="14" t="n">
         <v>12.32</v>
@@ -63303,10 +63303,10 @@
         <v>462</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="14" t="n">
         <v>28.06</v>
@@ -63406,10 +63406,10 @@
         <v>3237</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="14" t="n">
         <v>94.69</v>
@@ -63509,10 +63509,10 @@
         <v>1746.6</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="14" t="n">
         <v>241.92</v>
@@ -63612,10 +63612,10 @@
         <v>14563.8</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="14" t="n">
         <v>512.1799999999999</v>
@@ -63715,10 +63715,10 @@
         <v>2434.2</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="14" t="n">
         <v>712.98</v>
@@ -63818,10 +63818,10 @@
         <v>1863</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="14" t="n">
         <v>299.88</v>
@@ -63921,10 +63921,10 @@
         <v>159.6</v>
       </c>
       <c r="K27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="14" t="n">
         <v>14.39</v>
@@ -64024,10 +64024,10 @@
         <v>1160.4</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>41.47</v>
@@ -64127,10 +64127,10 @@
         <v>708</v>
       </c>
       <c r="K29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>21.08</v>
@@ -64230,10 +64230,10 @@
         <v>389.4</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="14" t="n">
         <v>23.04</v>
@@ -64333,10 +64333,10 @@
         <v>726.6</v>
       </c>
       <c r="K31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="14" t="n">
         <v>16.9</v>
@@ -64436,10 +64436,10 @@
         <v>8652</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>297.77</v>
@@ -64539,10 +64539,10 @@
         <v>4332.6</v>
       </c>
       <c r="K33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="14" t="n">
         <v>333.2</v>
@@ -64642,10 +64642,10 @@
         <v>2785.8</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="14" t="n">
         <v>135.52</v>
@@ -64745,10 +64745,10 @@
         <v>3174</v>
       </c>
       <c r="K35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="14" t="n">
         <v>645.5700000000001</v>
@@ -64848,10 +64848,10 @@
         <v>1678.2</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="14" t="n">
         <v>42.94</v>
@@ -64951,10 +64951,10 @@
         <v>2715</v>
       </c>
       <c r="K37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="14" t="n">
         <v>42.81</v>
@@ -65054,10 +65054,10 @@
         <v>3547.8</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="14" t="n">
         <v>60.32</v>
@@ -65157,10 +65157,10 @@
         <v>121.2</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="14" t="n">
         <v>0</v>
@@ -65260,10 +65260,10 @@
         <v>1218.6</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="14" t="n">
         <v>107.02</v>
@@ -65363,10 +65363,10 @@
         <v>8877.6</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" s="14" t="n">
         <v>482.16</v>
@@ -65466,10 +65466,10 @@
         <v>3243</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="14" t="n">
         <v>252</v>
@@ -65569,10 +65569,10 @@
         <v>640.8</v>
       </c>
       <c r="K43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="14" t="n">
         <v>0</v>
@@ -65672,10 +65672,10 @@
         <v>1182</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="14" t="n">
         <v>0</v>
@@ -65775,10 +65775,10 @@
         <v>8056.8</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="14" t="n">
         <v>211.33</v>
@@ -65878,10 +65878,10 @@
         <v>1378.2</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="14" t="n">
         <v>94.08</v>
@@ -65981,10 +65981,10 @@
         <v>8125.8</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="14" t="n">
         <v>996.76</v>
@@ -66084,10 +66084,10 @@
         <v>403.2</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="14" t="n">
         <v>29.4</v>
@@ -66187,10 +66187,10 @@
         <v>426</v>
       </c>
       <c r="K49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="14" t="n">
         <v>31.95</v>
@@ -66290,10 +66290,10 @@
         <v>3160.2</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="14" t="n">
         <v>346.47</v>
@@ -66393,10 +66393,10 @@
         <v>1113</v>
       </c>
       <c r="K51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="14" t="n">
         <v>53.04</v>
@@ -66496,10 +66496,10 @@
         <v>831</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="14" t="n">
         <v>31.95</v>
@@ -66599,10 +66599,10 @@
         <v>1872</v>
       </c>
       <c r="K53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="14" t="n">
         <v>36.1</v>
@@ -66702,10 +66702,10 @@
         <v>955.2</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="14" t="n">
         <v>140</v>
@@ -66805,10 +66805,10 @@
         <v>453</v>
       </c>
       <c r="K55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="14" t="n">
         <v>35.27</v>
@@ -66908,10 +66908,10 @@
         <v>1456.8</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="14" t="n">
         <v>47.93</v>
@@ -67011,10 +67011,10 @@
         <v>7157.4</v>
       </c>
       <c r="K57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="14" t="n">
         <v>511.39</v>
@@ -67114,10 +67114,10 @@
         <v>4069.8</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="14" t="n">
         <v>113.38</v>
@@ -67217,10 +67217,10 @@
         <v>492</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="14" t="n">
         <v>0</v>
@@ -67320,10 +67320,10 @@
         <v>2148.6</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="14" t="n">
         <v>26.94</v>
@@ -67423,10 +67423,10 @@
         <v>3624.6</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="14" t="n">
         <v>44.52</v>
@@ -67526,10 +67526,10 @@
         <v>2377.2</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="14" t="n">
         <v>42.6</v>
@@ -67629,10 +67629,10 @@
         <v>3589.8</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="14" t="n">
         <v>42.94</v>
@@ -67732,10 +67732,10 @@
         <v>229.8</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="14" t="n">
         <v>26.52</v>
@@ -67835,10 +67835,10 @@
         <v>630.6</v>
       </c>
       <c r="K65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="14" t="n">
         <v>38.7</v>
@@ -67938,10 +67938,10 @@
         <v>38.4</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="14" t="n">
         <v>0</v>
@@ -68041,10 +68041,10 @@
         <v>11.4</v>
       </c>
       <c r="K67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="14" t="n">
         <v>0</v>
@@ -68144,10 +68144,10 @@
         <v>106.8</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="14" t="n">
         <v>0</v>
@@ -68247,10 +68247,10 @@
         <v>556.8</v>
       </c>
       <c r="K69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="14" t="n">
         <v>0</v>
@@ -68350,10 +68350,10 @@
         <v>206.4</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="14" t="n">
         <v>0</v>
@@ -68453,10 +68453,10 @@
         <v>3802.2</v>
       </c>
       <c r="K71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="14" t="n">
         <v>308.26</v>
@@ -68556,10 +68556,10 @@
         <v>3993.6</v>
       </c>
       <c r="K72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="14" t="n">
         <v>547.74</v>
@@ -68659,10 +68659,10 @@
         <v>12469.2</v>
       </c>
       <c r="K73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="14" t="n">
         <v>432.22</v>
@@ -68762,10 +68762,10 @@
         <v>3237</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="14" t="n">
         <v>200.26</v>
@@ -68865,10 +68865,10 @@
         <v>6800.4</v>
       </c>
       <c r="K75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="14" t="n">
         <v>234.08</v>
@@ -68968,10 +68968,10 @@
         <v>2521.8</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="14" t="n">
         <v>397.13</v>
@@ -69071,10 +69071,10 @@
         <v>15269.4</v>
       </c>
       <c r="K77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="14" t="n">
         <v>1036.45</v>
@@ -69174,10 +69174,10 @@
         <v>934.8</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="14" t="n">
         <v>620.65</v>
@@ -69277,10 +69277,10 @@
         <v>13779</v>
       </c>
       <c r="K79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="14" t="n">
         <v>449.79</v>
@@ -69380,10 +69380,10 @@
         <v>387</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="14" t="n">
         <v>55.94</v>
@@ -69483,10 +69483,10 @@
         <v>12882</v>
       </c>
       <c r="K81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="14" t="n">
         <v>526.1799999999999</v>
@@ -69586,10 +69586,10 @@
         <v>9390</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>922.6799999999999</v>
@@ -69689,10 +69689,10 @@
         <v>16966.8</v>
       </c>
       <c r="K83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="14" t="n">
         <v>1108.89</v>
@@ -69792,10 +69792,10 @@
         <v>6364.2</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>0</v>
@@ -69895,10 +69895,10 @@
         <v>3172.2</v>
       </c>
       <c r="K85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="14" t="n">
         <v>319.2</v>
@@ -69998,10 +69998,10 @@
         <v>5683.2</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="14" t="n">
         <v>553.05</v>
@@ -70101,10 +70101,10 @@
         <v>8480.4</v>
       </c>
       <c r="K87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="14" t="n">
         <v>580.16</v>
@@ -70204,10 +70204,10 @@
         <v>5442.6</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="14" t="n">
         <v>612.7</v>
@@ -70307,10 +70307,10 @@
         <v>2920.2</v>
       </c>
       <c r="K89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="14" t="n">
         <v>417.76</v>
@@ -70410,10 +70410,10 @@
         <v>27458.4</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="14" t="n">
         <v>971.04</v>
@@ -70513,10 +70513,10 @@
         <v>14328.6</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="14" t="n">
         <v>716.8</v>
@@ -70616,10 +70616,10 @@
         <v>574.2</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>199.31</v>
@@ -70719,10 +70719,10 @@
         <v>9565.799999999999</v>
       </c>
       <c r="K93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="14" t="n">
         <v>281.28</v>
@@ -70822,10 +70822,10 @@
         <v>3690</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>441.5</v>
@@ -70925,10 +70925,10 @@
         <v>7170.6</v>
       </c>
       <c r="K95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="14" t="n">
         <v>449.79</v>
@@ -71028,10 +71028,10 @@
         <v>5788.8</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="14" t="n">
         <v>295.77</v>
@@ -71131,10 +71131,10 @@
         <v>2700.6</v>
       </c>
       <c r="K97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="14" t="n">
         <v>86.18000000000001</v>
@@ -71234,10 +71234,10 @@
         <v>6644.4</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="14" t="n">
         <v>275.22</v>
@@ -71337,10 +71337,10 @@
         <v>1964.4</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="14" t="n">
         <v>300.38</v>
@@ -71440,10 +71440,10 @@
         <v>1474.2</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" s="14" t="n">
         <v>128.8</v>
@@ -71543,10 +71543,10 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" s="14" t="n">
         <v>16.31</v>
@@ -71646,10 +71646,10 @@
         <v>3078</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>517.33</v>
@@ -71749,10 +71749,10 @@
         <v>162.6</v>
       </c>
       <c r="K103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103" s="14" t="n">
         <v>26.88</v>
@@ -71852,10 +71852,10 @@
         <v>10652.4</v>
       </c>
       <c r="K104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="14" t="n">
         <v>456.4</v>
@@ -71955,10 +71955,10 @@
         <v>3478.8</v>
       </c>
       <c r="K105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="14" t="n">
         <v>409.33</v>
@@ -72058,10 +72058,10 @@
         <v>936.6</v>
       </c>
       <c r="K106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="14" t="n">
         <v>253.79</v>
@@ -72161,10 +72161,10 @@
         <v>2715.6</v>
       </c>
       <c r="K107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="14" t="n">
         <v>0</v>
@@ -72264,10 +72264,10 @@
         <v>1450.8</v>
       </c>
       <c r="K108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="14" t="n">
         <v>57.51</v>
@@ -72367,10 +72367,10 @@
         <v>819</v>
       </c>
       <c r="K109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" s="14" t="n">
         <v>666.34</v>
@@ -72470,10 +72470,10 @@
         <v>156</v>
       </c>
       <c r="K110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="14" t="n">
         <v>5.19</v>
@@ -72573,10 +72573,10 @@
         <v>3368.4</v>
       </c>
       <c r="K111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="14" t="n">
         <v>514.25</v>
@@ -72676,10 +72676,10 @@
         <v>27196.2</v>
       </c>
       <c r="K112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" s="14" t="n">
         <v>787.54</v>
@@ -72779,10 +72779,10 @@
         <v>466.8</v>
       </c>
       <c r="K113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="14" t="n">
         <v>57.06</v>
@@ -72882,10 +72882,10 @@
         <v>2098.8</v>
       </c>
       <c r="K114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="14" t="n">
         <v>526.23</v>
@@ -72985,10 +72985,10 @@
         <v>8725.799999999999</v>
       </c>
       <c r="K115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="14" t="n">
         <v>360.42</v>
@@ -73088,10 +73088,10 @@
         <v>61855.8</v>
       </c>
       <c r="K116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L116" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M116" s="14" t="n">
         <v>1867.91</v>
@@ -73191,10 +73191,10 @@
         <v>227.4</v>
       </c>
       <c r="K117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" s="14" t="n">
         <v>8.4</v>
@@ -73294,10 +73294,10 @@
         <v>4406.4</v>
       </c>
       <c r="K118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="14" t="n">
         <v>658.5599999999999</v>
@@ -73397,10 +73397,10 @@
         <v>5078.4</v>
       </c>
       <c r="K119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="14" t="n">
         <v>836.66</v>
@@ -73500,10 +73500,10 @@
         <v>6370.8</v>
       </c>
       <c r="K120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="14" t="n">
         <v>211.06</v>
@@ -73603,10 +73603,10 @@
         <v>2863.8</v>
       </c>
       <c r="K121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="14" t="n">
         <v>120.51</v>
@@ -73706,10 +73706,10 @@
         <v>11926.8</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="14" t="n">
         <v>386.06</v>
@@ -73809,10 +73809,10 @@
         <v>1468.8</v>
       </c>
       <c r="K123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="14" t="n">
         <v>191.06</v>
@@ -73912,10 +73912,10 @@
         <v>9572.4</v>
       </c>
       <c r="K124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="14" t="n">
         <v>609.39</v>
@@ -74015,10 +74015,10 @@
         <v>6314.4</v>
       </c>
       <c r="K125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="14" t="n">
         <v>434.31</v>
@@ -74118,10 +74118,10 @@
         <v>2530.8</v>
       </c>
       <c r="K126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="14" t="n">
         <v>128.58</v>
@@ -74221,10 +74221,10 @@
         <v>3376.8</v>
       </c>
       <c r="K127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="14" t="n">
         <v>415.67</v>
@@ -74324,10 +74324,10 @@
         <v>6669.6</v>
       </c>
       <c r="K128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" s="14" t="n">
         <v>672.9</v>
@@ -74427,10 +74427,10 @@
         <v>463.2</v>
       </c>
       <c r="K129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="14" t="n">
         <v>289.52</v>
@@ -74530,10 +74530,10 @@
         <v>2230.2</v>
       </c>
       <c r="K130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="14" t="n">
         <v>147.62</v>
@@ -74633,10 +74633,10 @@
         <v>598.2</v>
       </c>
       <c r="K131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="14" t="n">
         <v>24.75</v>
@@ -74736,10 +74736,10 @@
         <v>2652.6</v>
       </c>
       <c r="K132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="14" t="n">
         <v>95.42</v>
@@ -74839,10 +74839,10 @@
         <v>790.2</v>
       </c>
       <c r="K133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" s="14" t="n">
         <v>448.56</v>
@@ -74942,10 +74942,10 @@
         <v>13406.4</v>
       </c>
       <c r="K134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="14" t="n">
         <v>504.31</v>
@@ -75045,10 +75045,10 @@
         <v>8152.8</v>
       </c>
       <c r="K135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="14" t="n">
         <v>313.04</v>
@@ -75148,10 +75148,10 @@
         <v>1092</v>
       </c>
       <c r="K136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" s="14" t="n">
         <v>23.5</v>
@@ -75251,10 +75251,10 @@
         <v>1350</v>
       </c>
       <c r="K137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="14" t="n">
         <v>17.2</v>
@@ -75354,10 +75354,10 @@
         <v>2592</v>
       </c>
       <c r="K138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="14" t="n">
         <v>45.2</v>
@@ -75457,10 +75457,10 @@
         <v>1344</v>
       </c>
       <c r="K139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" s="14" t="n">
         <v>11.8</v>
@@ -75560,10 +75560,10 @@
         <v>2112</v>
       </c>
       <c r="K140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="14" t="n">
         <v>23.5</v>
@@ -75663,10 +75663,10 @@
         <v>522</v>
       </c>
       <c r="K141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="14" t="n">
         <v>3.6</v>
@@ -75766,10 +75766,10 @@
         <v>948</v>
       </c>
       <c r="K142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="14" t="n">
         <v>6.7</v>
@@ -75869,10 +75869,10 @@
         <v>1698</v>
       </c>
       <c r="K143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="14" t="n">
         <v>15.2</v>
@@ -75972,10 +75972,10 @@
         <v>1344</v>
       </c>
       <c r="K144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="14" t="n">
         <v>13.5</v>
@@ -76075,10 +76075,10 @@
         <v>912</v>
       </c>
       <c r="K145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" s="14" t="n">
         <v>15.6</v>
